--- a/results/system_identification/24-09-20_sys_id_data_and_analysis.xlsx
+++ b/results/system_identification/24-09-20_sys_id_data_and_analysis.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\all my files\documents\uvm\5_masters\hive\github_directory\results\system_identification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\all my files\downloads_current\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8311B8D8-7736-4939-844F-120F832A6AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6F930A-33DB-4067-90E5-073F2446E836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4590" yWindow="16080" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{D62C10E0-EED1-4168-AB55-FA2294D53069}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="1" xr2:uid="{D62C10E0-EED1-4168-AB55-FA2294D53069}"/>
   </bookViews>
   <sheets>
     <sheet name="Chart1" sheetId="2" r:id="rId1"/>
     <sheet name="24-09-20_sys_id_data" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -11725,7 +11738,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-DB0C-4D7F-834F-9C5BBC9E597E}"/>
                   </c:ext>
@@ -13704,7 +13717,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-DB0C-4D7F-834F-9C5BBC9E597E}"/>
                   </c:ext>
